--- a/data/credit_bond_2026-07-29.xlsx
+++ b/data/credit_bond_2026-07-29.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-07-29" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-07-30" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -37,6 +37,10 @@
       <sz val="12.0"/>
       <color indexed="8"/>
       <b val="true"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="12.0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -90,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
@@ -99,6 +103,12 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
       <protection locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -149,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY1"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -163,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
     </row>
@@ -668,6 +678,231 @@
           <t>团费(%)</t>
         </is>
       </c>
+    </row>
+    <row r="3" customHeight="true" ht="18.0">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>26湖南银行债01</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>07-29 16:30</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>212680010.IB</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>25湖南银行债01</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>2.02Y</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>1.5812</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>1.5950/--</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>湖南银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>07-29 09:00</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>湖南省-长沙市</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。 </t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,东方证券股份有限公司,中国银行股份有限公司,兴业银行股份有限公司,华夏银行股份有限公司,恒丰银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>湖南银行股份有限公司2026年第一期金融债券</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>2029-07-31</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>城商行</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AY3" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-07-29.xlsx
+++ b/data/credit_bond_2026-07-29.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-07-30" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-07-31" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -37,10 +37,6 @@
       <sz val="12.0"/>
       <color indexed="8"/>
       <b val="true"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <sz val="12.0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -94,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
@@ -103,12 +99,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
       <protection locked="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -159,7 +149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY1"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -173,252 +163,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
     </row>
@@ -678,231 +668,6 @@
           <t>团费(%)</t>
         </is>
       </c>
-    </row>
-    <row r="3" customHeight="true" ht="18.0">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>26湖南银行债01</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>07-29 16:30</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>212680010.IB</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>3Y</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>70.0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>70.0</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>1.30 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>30.59</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>25湖南银行债01</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>2.02Y</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>1.5812</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>1.5950/--</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>湖南银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>07-29 09:00</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>1.63%~1.73%</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>湖南省-长沙市</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。 </t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr">
-        <is>
-          <t>中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,东方证券股份有限公司,中国银行股份有限公司,兴业银行股份有限公司,华夏银行股份有限公司,恒丰银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>商业银行普通债券</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="AF3" s="3" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="AG3" s="3" t="inlineStr">
-        <is>
-          <t>湖南银行股份有限公司2026年第一期金融债券</t>
-        </is>
-      </c>
-      <c r="AH3" s="3" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="AI3" s="3" t="inlineStr">
-        <is>
-          <t>2029-07-31</t>
-        </is>
-      </c>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AM3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AQ3" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>城商行</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AY3" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-07-29.xlsx
+++ b/data/credit_bond_2026-07-29.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-07-31" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-03" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -37,6 +37,10 @@
       <sz val="12.0"/>
       <color indexed="8"/>
       <b val="true"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="12.0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -90,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
@@ -99,6 +103,12 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
       <protection locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -149,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY1"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -163,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
     </row>
@@ -668,6 +678,235 @@
           <t>团费(%)</t>
         </is>
       </c>
+    </row>
+    <row r="3" customHeight="true" ht="18.0">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>26农业银行绿色债01</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>08-03 18:00</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2628001.IB</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>1.20 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>25农业银行绿色债02</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>3.57Y</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>1.5338</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>中国农业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>08-03 09:00</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>1.52%~1.62%</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,华泰证券股份有限公司,招商证券股份有限公司,中银国际证券股份有限公司,国投证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>中央国有企业</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>中国农业银行股份有限公司2026年绿色金融债券(第一期)(债券通)</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>2029-08-05</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>国有银行</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AY3" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-07-29.xlsx
+++ b/data/credit_bond_2026-07-29.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4700</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">

--- a/data/credit_bond_2026-07-29.xlsx
+++ b/data/credit_bond_2026-07-29.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-03" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-04" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-03</t>
+          <t>数据来源：DM    2026-08-04</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/1.4700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
